--- a/Key Documents/90 Day Decision Log - Carson Froy and Kain Kim.xlsx
+++ b/Key Documents/90 Day Decision Log - Carson Froy and Kain Kim.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9E9BA3834382A0EF/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="8_{37764FF7-839F-4202-AA63-04F5FFC23D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8962E81C-A689-42EA-8CC7-88F3CB02DD46}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="8_{37764FF7-839F-4202-AA63-04F5FFC23D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{714F6799-6802-4B8B-B868-34FB58B0161D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,7 +328,7 @@
     <t>Offseason</t>
   </si>
   <si>
-    <t>Players in the offseason typically have lower markets, which usually rise once the preaseason begins. I believe that this card will not only jump in the preseason, but based on his performace as a rookie, along with his increased target share due to the signing of Mike Evans to the 49ers, which opens up a large volume of targets for the current Buccaneers WRs</t>
+    <t>Players in the offseason typically have lower markets, which usually rise once the preaseason begins. I believe that this card will not only jump in the preseason, but based on his performace as a rookie, along with his increased target share due to the signing of Mike Evans to the 49ers, which opens up a large volume of targets for the current Buccaneers WRs. Season Projections: Receptions: 65 - 70 Receiving Yards: 900 - 1,000Touchdowns: 5 - 7. Last season stats: Receptions: 63 Receiving Yards: 938 Touchdowns: 6</t>
   </si>
   <si>
     <t>Price increase to ~$100, Egbuka sees the expected increase in targets and has explosive performances, which increases his overall market.</t>
@@ -454,7 +454,7 @@
     <t>$245.00 5/31/2026</t>
   </si>
   <si>
-    <t>Burden is set to have an increased role in the Bears offense this season with the departure of former #1 WR DJ Moore being traded. Burden exploded late in the season and is poised for an even bigger sophomore year. Burden is in the offseason currently, which means that the football card market as a whole is lower than it will be at the start of the season.</t>
+    <t>Burden is set to have an increased role in the Bears offense this season with the departure of former #1 WR DJ Moore being traded. Burden exploded late in the season and is poised for an even bigger sophomore year. Burden is in the offseason currently, which means that the football card market as a whole is lower than it will be at the start of the season.Projected Range: Receptions 73 – 75 Receiving Yards 950 – 980  Touchdowns 5 – 6. Last season stats: Receptions 47 Receiving Yards 652 Touchdowns 2</t>
   </si>
   <si>
     <t>Preaseason spike to ~$300, or a mid season breakout causes the card to climb into the mid $300s.</t>
@@ -600,7 +600,7 @@
     <numFmt numFmtId="164" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -813,9 +813,6 @@
     <xf numFmtId="8" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -825,7 +822,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1091,234 +1091,249 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:6" ht="23.25">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-    </row>
-    <row r="4" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+    </row>
+    <row r="4" spans="1:6" ht="16.5">
+      <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-    </row>
-    <row r="5" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="1:6" ht="45" customHeight="1">
+      <c r="A5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-    </row>
-    <row r="7" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+    </row>
+    <row r="7" spans="1:6" ht="16.5">
+      <c r="A7" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-    </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:6" ht="30" customHeight="1">
+      <c r="A8" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+    </row>
+    <row r="9" spans="1:6" ht="30" customHeight="1">
+      <c r="A9" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+    </row>
+    <row r="10" spans="1:6" ht="18" customHeight="1">
+      <c r="A10" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1">
+      <c r="A11" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+    </row>
+    <row r="12" spans="1:6" ht="18" customHeight="1">
+      <c r="A12" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+    </row>
+    <row r="14" spans="1:6" ht="16.5">
+      <c r="A14" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-    </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="23" t="s">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+    </row>
+    <row r="15" spans="1:6" ht="18" customHeight="1">
+      <c r="A15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1">
+      <c r="A16" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1">
+      <c r="A17" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="22" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+    </row>
+    <row r="19" spans="1:6" ht="16.5">
+      <c r="A19" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1">
+      <c r="A20" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+    </row>
+    <row r="21" spans="1:6" ht="18" customHeight="1">
+      <c r="A21" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-    </row>
-    <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" spans="1:6" ht="18" customHeight="1">
+      <c r="A22" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-    </row>
-    <row r="23" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+    </row>
+    <row r="23" spans="1:6" ht="18" customHeight="1">
+      <c r="A23" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+    </row>
+    <row r="24" spans="1:6" ht="18" customHeight="1">
+      <c r="A24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-    </row>
-    <row r="26" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+    </row>
+    <row r="26" spans="1:6" ht="16.5">
+      <c r="A26" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-    </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+    </row>
+    <row r="27" spans="1:6" ht="30" customHeight="1">
+      <c r="A27" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A20:F20"/>
@@ -1326,21 +1341,6 @@
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1350,7 +1350,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -1358,15 +1358,15 @@
     <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:4" ht="23.25">
+      <c r="A1" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-    </row>
-    <row r="3" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+    </row>
+    <row r="3" spans="1:4" ht="42" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="276.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="276.75" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="90" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -1402,7 +1402,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="90" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
@@ -1410,7 +1410,7 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="90" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
@@ -1430,7 +1430,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W35"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
@@ -1451,33 +1451,33 @@
     <col min="23" max="23" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:23" ht="23.25">
+      <c r="A1" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-    </row>
-    <row r="3" spans="1:23" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+    </row>
+    <row r="3" spans="1:23" ht="42" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="90" customHeight="1">
       <c r="A4" s="17">
         <v>46168</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="90" customHeight="1">
       <c r="A5" s="17">
         <v>46168</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="177.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="177.75" customHeight="1">
       <c r="A6" s="17">
         <v>46169</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="177" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="177" customHeight="1">
       <c r="A7" s="17">
         <v>46169</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="188.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" ht="188.25" customHeight="1">
       <c r="A8" s="17">
         <v>46170</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="148.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="148.5" customHeight="1">
       <c r="A9" s="17">
         <v>46175</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" ht="60" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1993,7 +1993,7 @@
       <c r="V10" s="2"/>
       <c r="W10" s="4"/>
     </row>
-    <row r="11" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="60" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2018,7 +2018,7 @@
       <c r="V11" s="2"/>
       <c r="W11" s="4"/>
     </row>
-    <row r="12" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="60" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2043,7 +2043,7 @@
       <c r="V12" s="2"/>
       <c r="W12" s="4"/>
     </row>
-    <row r="13" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="60" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2068,7 +2068,7 @@
       <c r="V13" s="2"/>
       <c r="W13" s="4"/>
     </row>
-    <row r="14" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="60" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2093,7 +2093,7 @@
       <c r="V14" s="2"/>
       <c r="W14" s="4"/>
     </row>
-    <row r="15" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" ht="60" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2118,7 +2118,7 @@
       <c r="V15" s="2"/>
       <c r="W15" s="4"/>
     </row>
-    <row r="16" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="60" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2143,7 +2143,7 @@
       <c r="V16" s="2"/>
       <c r="W16" s="4"/>
     </row>
-    <row r="17" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="60" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2168,7 +2168,7 @@
       <c r="V17" s="2"/>
       <c r="W17" s="4"/>
     </row>
-    <row r="18" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" ht="60" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2193,7 +2193,7 @@
       <c r="V18" s="2"/>
       <c r="W18" s="4"/>
     </row>
-    <row r="19" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" ht="60" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2218,7 +2218,7 @@
       <c r="V19" s="2"/>
       <c r="W19" s="4"/>
     </row>
-    <row r="20" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="60" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2243,7 +2243,7 @@
       <c r="V20" s="2"/>
       <c r="W20" s="4"/>
     </row>
-    <row r="21" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" ht="60" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2268,7 +2268,7 @@
       <c r="V21" s="2"/>
       <c r="W21" s="4"/>
     </row>
-    <row r="22" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" ht="60" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2293,7 +2293,7 @@
       <c r="V22" s="2"/>
       <c r="W22" s="4"/>
     </row>
-    <row r="23" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="60" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2318,7 +2318,7 @@
       <c r="V23" s="2"/>
       <c r="W23" s="4"/>
     </row>
-    <row r="24" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="60" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2343,7 +2343,7 @@
       <c r="V24" s="2"/>
       <c r="W24" s="4"/>
     </row>
-    <row r="25" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="60" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2368,7 +2368,7 @@
       <c r="V25" s="2"/>
       <c r="W25" s="4"/>
     </row>
-    <row r="26" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="60" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2393,7 +2393,7 @@
       <c r="V26" s="2"/>
       <c r="W26" s="4"/>
     </row>
-    <row r="27" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="60" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2418,7 +2418,7 @@
       <c r="V27" s="2"/>
       <c r="W27" s="4"/>
     </row>
-    <row r="28" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="60" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2443,7 +2443,7 @@
       <c r="V28" s="2"/>
       <c r="W28" s="4"/>
     </row>
-    <row r="29" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="60" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2468,7 +2468,7 @@
       <c r="V29" s="2"/>
       <c r="W29" s="4"/>
     </row>
-    <row r="30" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="60" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2493,7 +2493,7 @@
       <c r="V30" s="2"/>
       <c r="W30" s="4"/>
     </row>
-    <row r="31" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="60" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2518,7 +2518,7 @@
       <c r="V31" s="2"/>
       <c r="W31" s="4"/>
     </row>
-    <row r="32" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="60" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2543,7 +2543,7 @@
       <c r="V32" s="2"/>
       <c r="W32" s="4"/>
     </row>
-    <row r="33" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" ht="60" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2568,7 +2568,7 @@
       <c r="V33" s="2"/>
       <c r="W33" s="4"/>
     </row>
-    <row r="34" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" ht="60" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2593,7 +2593,7 @@
       <c r="V34" s="2"/>
       <c r="W34" s="4"/>
     </row>
-    <row r="35" spans="1:23" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" ht="60" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2644,7 +2644,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P29"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
@@ -2660,23 +2660,23 @@
     <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:16" ht="23.25">
+      <c r="A1" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-    </row>
-    <row r="3" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="3" spans="1:16" ht="42" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>127</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="79.5" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="60" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2776,7 +2776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" ht="60" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2804,7 +2804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="60" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2832,7 +2832,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="60" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2860,7 +2860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" ht="60" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2888,7 +2888,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="60" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2909,7 +2909,7 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="60" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2930,7 +2930,7 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
     </row>
-    <row r="12" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="60" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2951,7 +2951,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="60" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2972,7 +2972,7 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="60" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2993,7 +2993,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="60" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -3014,7 +3014,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="60" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -3035,7 +3035,7 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
     </row>
-    <row r="17" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="60" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -3056,7 +3056,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
     </row>
-    <row r="18" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="60" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -3077,7 +3077,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="60" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -3098,7 +3098,7 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
     </row>
-    <row r="20" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="60" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3119,7 +3119,7 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="60" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -3140,7 +3140,7 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="60" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -3161,7 +3161,7 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="60" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3182,7 +3182,7 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="60" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3203,7 +3203,7 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="60" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3224,7 +3224,7 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="60" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3245,7 +3245,7 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="60" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3266,7 +3266,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="60" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3287,7 +3287,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="60" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3320,7 +3320,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -3330,27 +3330,27 @@
     <col min="6" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:6" ht="23.25">
+      <c r="A1" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-    </row>
-    <row r="2" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+    </row>
+    <row r="2" spans="1:6" ht="31.5" customHeight="1">
+      <c r="A2" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-    </row>
-    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+    </row>
+    <row r="4" spans="1:6" ht="42" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>149</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="60" customHeight="1">
       <c r="A5" s="13">
         <v>1</v>
       </c>
@@ -3380,7 +3380,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="60" customHeight="1">
       <c r="A6" s="13">
         <v>2</v>
       </c>
@@ -3390,7 +3390,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="60" customHeight="1">
       <c r="A7" s="13">
         <v>3</v>
       </c>
@@ -3400,7 +3400,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="60" customHeight="1">
       <c r="A8" s="13">
         <v>4</v>
       </c>
@@ -3410,7 +3410,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="60" customHeight="1">
       <c r="A9" s="13">
         <v>5</v>
       </c>
@@ -3420,7 +3420,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="60" customHeight="1">
       <c r="A10" s="13">
         <v>6</v>
       </c>
@@ -3430,7 +3430,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="60" customHeight="1">
       <c r="A11" s="13">
         <v>7</v>
       </c>
@@ -3440,7 +3440,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="60" customHeight="1">
       <c r="A12" s="13">
         <v>8</v>
       </c>
@@ -3450,7 +3450,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="60" customHeight="1">
       <c r="A13" s="13">
         <v>9</v>
       </c>
@@ -3460,7 +3460,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="60" customHeight="1">
       <c r="A14" s="13">
         <v>10</v>
       </c>
@@ -3470,7 +3470,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="60" customHeight="1">
       <c r="A15" s="13">
         <v>11</v>
       </c>
@@ -3480,7 +3480,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="60" customHeight="1">
       <c r="A16" s="13">
         <v>12</v>
       </c>
@@ -3490,7 +3490,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="60" customHeight="1">
       <c r="A17" s="13">
         <v>13</v>
       </c>
@@ -3513,21 +3513,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="4" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:4" ht="23.25">
+      <c r="A1" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="26" t="s">
         <v>155</v>
       </c>
@@ -3535,7 +3535,7 @@
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
     </row>
-    <row r="4" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="42" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>156</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="109.5" customHeight="1">
       <c r="A5" s="14" t="s">
         <v>160</v>
       </c>
@@ -3557,7 +3557,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="109.5" customHeight="1">
       <c r="A6" s="14" t="s">
         <v>161</v>
       </c>
@@ -3565,7 +3565,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="109.5" customHeight="1">
       <c r="A7" s="14" t="s">
         <v>162</v>
       </c>
@@ -3573,7 +3573,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="109.5" customHeight="1">
       <c r="A8" s="14" t="s">
         <v>163</v>
       </c>
@@ -3581,7 +3581,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="109.5" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>164</v>
       </c>
@@ -3589,7 +3589,7 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="109.5" customHeight="1">
       <c r="A10" s="14" t="s">
         <v>165</v>
       </c>
@@ -3597,7 +3597,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="109.5" customHeight="1">
       <c r="A11" s="14" t="s">
         <v>166</v>
       </c>
